--- a/Practice/01_TSoverview/01-introTS-FC.xlsx
+++ b/Practice/01_TSoverview/01-introTS-FC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS8711\Practice\01_TSoverview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B1F3BA-A3BD-4783-9A7F-3BF2DC54DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41BE623-E20D-4EC2-B552-B853D288ED0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D17E8219-D62D-42DE-9174-AFE1C10CFFFF}"/>
   </bookViews>
@@ -976,7 +976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -994,6 +994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
@@ -1048,8 +1049,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="457200" y="2114550"/>
-          <a:ext cx="4236042" cy="968511"/>
+          <a:off x="1676400" y="2105025"/>
+          <a:ext cx="4169367" cy="1025661"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7128,6 +7129,7 @@
         <v>45</v>
       </c>
     </row>
+    <row r="3" spans="1:45" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>251</v>
@@ -7135,6 +7137,9 @@
       <c r="D4">
         <v>0.30220156510396212</v>
       </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
@@ -7159,7 +7164,7 @@
         <v>41.949116298105743</v>
       </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
@@ -7437,7 +7442,7 @@
         <v>0.60440313020792424</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" ref="M9:M11" si="3">L9*J9</f>
+        <f t="shared" ref="M9:M10" si="3">L9*J9</f>
         <v>36.694293035629507</v>
       </c>
       <c r="Q9" t="s">
@@ -8242,6 +8247,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4F846F99B6B8D428F9F7C242A6AB43C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b73aa369982c0e65af77f8cfa86d2807">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b943f129-a7cc-4119-8885-bafc764d2a65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4651074ac392566ed8a2bce3b6e12e1d" ns2:_="">
     <xsd:import namespace="b943f129-a7cc-4119-8885-bafc764d2a65"/>
@@ -8379,22 +8399,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6154A2B7-00EC-4D14-887A-4AA532A425A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990A64B7-319D-4A67-8D54-85E0542EF5BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C8AE1A8-9684-4FCB-90B7-21F65B061956}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8410,21 +8432,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990A64B7-319D-4A67-8D54-85E0542EF5BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6154A2B7-00EC-4D14-887A-4AA532A425A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>